--- a/docs/测试/04-功能验收校验清单与上线合规检查表.xlsx
+++ b/docs/测试/04-功能验收校验清单与上线合规检查表.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>修改密码需校验旧密码，改后旧密码失效</t>
+          <t>修改密码需校验旧密码、新密码不少于 8 位，改后旧密码失效</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>商品主图支持 jpg/png/gif/webp 且限制 5MB</t>
+          <t>商品主图仅支持 JPG/PNG 且单张不超过 5MB</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">

--- a/docs/测试/04-功能验收校验清单与上线合规检查表.xlsx
+++ b/docs/测试/04-功能验收校验清单与上线合规检查表.xlsx
@@ -3583,12 +3583,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>本地单机接口响应时间观测</t>
+          <t>对主路径接口多次采样测量响应耗时</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>响应时间 &lt; 2 秒</t>
+          <t>各次响应耗时 &lt; 2 秒</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>本地单机全部接口响应远低于 2 秒；未做压力与长时间稳定性测试，NFR-007（可用性≥99%）无法在课程环境验证。</t>
+          <t>TC-L01~TC-L04 通过：商品详情、在售状态、卖家后台列表、凭口令码查询多次采样的耗时均远低于 2 秒；未做压力与长时间稳定性测试，NFR-007（可用性≥99%）无法在课程环境验证。</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>仓库自带 pytest 28 条全部通过；本轮补充黑盒功能测试 113 条（通过率 98.2%）。</t>
+          <t>仓库自带 pytest 28 条全部通过；本轮补充黑盒功能测试 117 条（通过率 98.3%）。</t>
         </is>
       </c>
     </row>
